--- a/UserScore/PersonalUsers.xlsx
+++ b/UserScore/PersonalUsers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,22 @@
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8502504224</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>O000000000O00000000O</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Nimish</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/UserScore/PersonalUsers.xlsx
+++ b/UserScore/PersonalUsers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,8 +451,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>6402685128</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6402685128</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -471,8 +473,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>8068933555</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>8068933555</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
@@ -483,8 +487,10 @@
       <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>6852545266</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>6852545266</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -503,8 +509,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>5825517851</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>5825517851</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
@@ -515,8 +523,10 @@
       <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>6604290522</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6604290522</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -531,8 +541,10 @@
       <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>8502504224</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>8502504224</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -545,6 +557,586 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>6583378153</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>jjo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1585511136</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bharaman</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Boys</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7362333909</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Phina 🔥🙈</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8069950420</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ashuchoudhary03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ashish</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Choudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>787206761</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cop_suraj_saroj</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Suraj</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Saroj</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>8534931118</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Rohit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>7041186172</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Koket🐾</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>8088573230</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ጵንኤል</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>7162191833</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trust</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>The process ⏳</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>8320579025</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Om</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bhawar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>5080276560</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BhaKth_bH0lenath_ka</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>8366572154</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>RUHI</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>5939779103</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Idne3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AKC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>5196821827</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>كمالة🌹🌹🌹</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8548633397</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Lovely girl</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1489390921</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A.Y🥀</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8218040960</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bee_dib</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>7503566294</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sif2763</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>✨Abdii°✨</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>6996526704</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aott4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>𝖙𝖍𝖊 𝖐𝖎𝖓𝖌 𝖔𝖋 𝖕𝖎𝖌</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>8496827721</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Webigentleman</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ŵæbii 🔥🔥</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>7724635562</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Karan</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5846833139</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>withoutgoal2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Lifeless</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>7284303665</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>pcl_aw</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Picok</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>8479806647</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8317268321</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rebecca</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Taiwo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>8351976888</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Riteghan</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Hasone</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>8106678668</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Samod</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Abdulfatai</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6399748370</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Klmp698</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6549843031</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>zaha_185</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>~</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7438830445</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Keol</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Abe</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7129259981</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Primevicc</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Oluwanifemi</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>💓💓💓</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>6371497376</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Joy</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7225008655</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Rewan</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rady</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7266508386</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Mistah_Leo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Uzøhő Çĥînédum Łionël</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Jr 🥶🥶🥶</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/UserScore/PersonalUsers.xlsx
+++ b/UserScore/PersonalUsers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,214 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>6884994120</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>johndibab</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1197712070</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Cloud غيمة فرح</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7039277814</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>John Dibab</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7869483072</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Sc_Jax</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>𝐒𝐂</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>6216506341</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Curiousgirl25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Sweety ✨✨</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6152137422</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Radha</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>8129284239</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sen</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>8430879958</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NAARAH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>5209644377</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pratyushtiwari7</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>..pratyush</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>8361785246</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Efrata_2130</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>......🦋✨️</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1704270851</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mr_PH0ENIX</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ᴍr.🅿🅷🅾🅴🅽🅸🆇 ㅤㅤㅤㅤㅤㅤㅤㅤᴬᵈᵐⁱⁿ</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>5951027441</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>redwan5524</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>𝐍 𝐠𝐢𝐯𝐞 𝐮𝐩®</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
